--- a/source/bin/excel/outfit_config.xlsx
+++ b/source/bin/excel/outfit_config.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\liqi-excel\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4875F25E-CD5B-445B-BD2B-CC9E60CE50FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EA0C8D9-A39F-43E2-8A2E-D84C8AD076AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="export" sheetId="2" r:id="rId1"/>
@@ -80,7 +80,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="49">
   <si>
     <t>sheet</t>
   </si>
@@ -236,6 +236,26 @@
   </si>
   <si>
     <t>和牌-咒层界・恶念祝祭</t>
+  </si>
+  <si>
+    <t>hide_direction</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>部分方向隐藏特效</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>liqi_25yh眼镜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,0,1,0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -302,9 +322,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1004,31 +1027,57 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6385CBF5-A086-48A6-8782-0BA91FDDA6E5}">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="13.125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="14.875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="16.375" style="2" customWidth="1"/>
+    <col min="4" max="16384" width="9" style="2"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+      <c r="B1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+      <c r="C2" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="2" t="s">
         <v>11</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B4" s="2">
+        <v>308048</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>

--- a/source/bin/excel/outfit_config.xlsx
+++ b/source/bin/excel/outfit_config.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\liqi-excel\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\quehun-cehua\liqi-excel\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EA0C8D9-A39F-43E2-8A2E-D84C8AD076AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BECC03F1-ABFC-4E1C-8F24-61C99168D5C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="export" sheetId="2" r:id="rId1"/>
@@ -45,10 +45,35 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
+    <author>tatara yomon</author>
     <author>晓楠</author>
   </authors>
   <commentList>
-    <comment ref="D2" authorId="0" shapeId="0" xr:uid="{D5C0DA37-2E9F-4AAB-8609-C5CDCCAD2DDD}">
+    <comment ref="C2" authorId="0" shapeId="0" xr:uid="{3489155F-F7CD-4AEC-92B6-F27DAECFE345}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>叶子猹:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+原laya专用的字段，已废除</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D2" authorId="1" shapeId="0" xr:uid="{D5C0DA37-2E9F-4AAB-8609-C5CDCCAD2DDD}">
       <text>
         <r>
           <rPr>
@@ -80,7 +105,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="50">
   <si>
     <t>sheet</t>
   </si>
@@ -255,6 +280,10 @@
   </si>
   <si>
     <t>1,0,1,0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>和牌-神火坠霄</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -262,7 +291,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -298,6 +327,19 @@
       <color indexed="81"/>
       <name val="宋体"/>
       <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -344,6 +386,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -801,12 +847,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25BFD0D9-A731-4E37-9AB5-66B1A0F6E359}">
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="22.25" customWidth="1"/>
     <col min="2" max="2" width="17.375" customWidth="1"/>
-    <col min="3" max="3" width="26" customWidth="1"/>
+    <col min="3" max="3" width="26" hidden="1" customWidth="1"/>
     <col min="4" max="4" width="18.875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -977,6 +1023,20 @@
       </c>
       <c r="D14">
         <v>1860</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>49</v>
+      </c>
+      <c r="B15">
+        <v>30520013</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15">
+        <v>5000</v>
       </c>
     </row>
   </sheetData>
